--- a/Datas/TaskScheduleModelDataList.xlsx
+++ b/Datas/TaskScheduleModelDataList.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>TaskScheduleModelEditorData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,6 +57,41 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
+    <t>看守柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家里闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0,20,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,0,24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌晨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -384,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -448,8 +483,147 @@
         <v>8</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>2002</v>
+      </c>
+      <c r="F4">
+        <v>1000</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>2001</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>2002</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>2001</v>
+      </c>
+      <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>2000</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>2000</v>
+      </c>
+      <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/TaskScheduleModelDataList.xlsx
+++ b/Datas/TaskScheduleModelDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
   <si>
     <t>TaskScheduleModelEditorData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,6 +130,22 @@
   </si>
   <si>
     <t>逛街</t>
+  </si>
+  <si>
+    <t>早上无柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白天无柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白天无柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上无柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -458,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -829,6 +845,221 @@
       </c>
       <c r="G16">
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP(D17,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2002</v>
+      </c>
+      <c r="F17">
+        <v>1000</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP(D18,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2002</v>
+      </c>
+      <c r="F18">
+        <v>1000</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP(D19,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2003</v>
+      </c>
+      <c r="F19">
+        <v>1000</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP(D20,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2004</v>
+      </c>
+      <c r="F20">
+        <v>1000</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP(D21,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2005</v>
+      </c>
+      <c r="F21">
+        <v>1000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP(D22,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2006</v>
+      </c>
+      <c r="F22">
+        <v>1000</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP(D23,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2007</v>
+      </c>
+      <c r="F23">
+        <v>1000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>12</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP(D24,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2002</v>
+      </c>
+      <c r="F24">
+        <v>1000</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>12</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>2000</v>
+      </c>
+      <c r="F25">
+        <v>1000</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TaskScheduleModelDataList.xlsx
+++ b/Datas/TaskScheduleModelDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
   <si>
     <t>TaskScheduleModelEditorData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,6 +145,10 @@
   </si>
   <si>
     <t>晚上无柜台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作地点闲逛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -588,20 +592,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <f>VLOOKUP(D6,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -621,11 +624,11 @@
         <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <f>VLOOKUP(D7,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -645,11 +648,10 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <f>VLOOKUP(D8,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F8">
         <v>1000</v>
@@ -669,11 +671,11 @@
         <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <f>VLOOKUP(D9,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F9">
         <v>1000</v>
@@ -693,11 +695,11 @@
         <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10">
         <f>VLOOKUP(D10,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F10">
         <v>1000</v>
@@ -717,11 +719,11 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <f>VLOOKUP(D11,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="F11">
         <v>1000</v>
@@ -741,11 +743,11 @@
         <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12">
         <f>VLOOKUP(D12,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F12">
         <v>1000</v>
@@ -754,54 +756,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <f>VLOOKUP(D13,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="F13">
         <v>1000</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E14">
-        <v>2001</v>
+        <f>VLOOKUP(D14,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2007</v>
       </c>
       <c r="F14">
         <v>1000</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -812,105 +815,103 @@
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15">
-        <v>2000</v>
+        <f>VLOOKUP(D15,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2002</v>
       </c>
       <c r="F15">
         <v>1000</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>3</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="F16">
         <v>1000</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17">
-        <f>VLOOKUP(D17,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F17">
         <v>1000</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <f>VLOOKUP(D18,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="F18">
         <v>1000</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <f>VLOOKUP(D19,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="F19">
         <v>1000</v>
@@ -921,20 +922,20 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <f>VLOOKUP(D20,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F20">
         <v>1000</v>
@@ -945,20 +946,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E21">
-        <f>VLOOKUP(D21,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="F21">
         <v>1000</v>
@@ -978,11 +978,11 @@
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <f>VLOOKUP(D22,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="F22">
         <v>1000</v>
@@ -996,17 +996,16 @@
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <f>VLOOKUP(D23,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F23">
         <v>1000</v>
@@ -1017,49 +1016,192 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E24">
         <f>VLOOKUP(D24,Sheet1!$D$3:$E$10,2,FALSE)</f>
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F24">
         <v>1000</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <f>VLOOKUP(D25,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2004</v>
+      </c>
+      <c r="F25">
+        <v>1000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <f>VLOOKUP(D26,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2005</v>
+      </c>
+      <c r="F26">
+        <v>1000</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27">
+        <f>VLOOKUP(D27,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2006</v>
+      </c>
+      <c r="F27">
+        <v>1000</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28">
+        <f>VLOOKUP(D28,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2007</v>
+      </c>
+      <c r="F28">
+        <v>1000</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>12</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C29" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29">
+        <f>VLOOKUP(D29,Sheet1!$D$3:$E$10,2,FALSE)</f>
+        <v>2002</v>
+      </c>
+      <c r="F29">
+        <v>1000</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>12</v>
       </c>
-      <c r="E25">
+      <c r="B30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30">
         <v>2000</v>
       </c>
-      <c r="F25">
-        <v>1000</v>
-      </c>
-      <c r="G25">
+      <c r="F30">
+        <v>1000</v>
+      </c>
+      <c r="G30">
         <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>12</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31">
+        <v>2008</v>
+      </c>
+      <c r="F31">
+        <v>1000</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TaskScheduleModelDataList.xlsx
+++ b/Datas/TaskScheduleModelDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="46">
   <si>
     <t>TaskScheduleModelEditorData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,6 +149,42 @@
   </si>
   <si>
     <t>工作地点闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物白天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物晚上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0,20,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窝里闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场地闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物深夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物晚上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物睡眠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -478,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" style="1" customWidth="1"/>
@@ -1202,6 +1238,144 @@
       </c>
       <c r="G31">
         <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>20</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32">
+        <v>2009</v>
+      </c>
+      <c r="F32">
+        <v>1000</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>20</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33">
+        <v>2010</v>
+      </c>
+      <c r="F33">
+        <v>1000</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>20</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34">
+        <v>2011</v>
+      </c>
+      <c r="F34">
+        <v>1000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>21</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35">
+        <v>2009</v>
+      </c>
+      <c r="F35">
+        <v>1000</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>21</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36">
+        <v>2012</v>
+      </c>
+      <c r="F36">
+        <v>1000</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>22</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37">
+        <v>2012</v>
+      </c>
+      <c r="F37">
+        <v>1000</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TaskScheduleModelDataList.xlsx
+++ b/Datas/TaskScheduleModelDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="48">
   <si>
     <t>TaskScheduleModelEditorData</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,19 +168,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>吃东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物深夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物晚上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物睡眠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窝里闲逛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>场地闲逛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吃东西</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>动物深夜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>动物晚上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1251,7 +1259,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E32">
         <v>2009</v>
@@ -1274,7 +1282,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E33">
         <v>2010</v>
@@ -1297,7 +1305,7 @@
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34">
         <v>2011</v>
@@ -1337,13 +1345,13 @@
         <v>21</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E36">
         <v>2012</v>
@@ -1360,13 +1368,13 @@
         <v>22</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37">
         <v>2012</v>
